--- a/reports/China_3.1.2_top_import_partners_cols.xlsx
+++ b/reports/China_3.1.2_top_import_partners_cols.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="190">
   <si>
     <t>reporterDesc</t>
   </si>
@@ -941,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:NF14"/>
+  <dimension ref="A1:NF15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:370">
@@ -14668,6 +14668,1118 @@
         <v>1285978735.608</v>
       </c>
     </row>
+    <row r="15" spans="1:370">
+      <c r="A15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>1.270305929210625E-10</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.3136146254626668</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0.001577401445663284</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0.005824198945948584</v>
+      </c>
+      <c r="CB15">
+        <v>0.0006199019597379141</v>
+      </c>
+      <c r="CC15">
+        <v>0</v>
+      </c>
+      <c r="CD15">
+        <v>0.2101951689755873</v>
+      </c>
+      <c r="CE15">
+        <v>0</v>
+      </c>
+      <c r="CF15">
+        <v>0</v>
+      </c>
+      <c r="CG15">
+        <v>0</v>
+      </c>
+      <c r="CH15">
+        <v>0</v>
+      </c>
+      <c r="CI15">
+        <v>0</v>
+      </c>
+      <c r="CJ15">
+        <v>0.3776983134661701</v>
+      </c>
+      <c r="CK15">
+        <v>0</v>
+      </c>
+      <c r="CL15">
+        <v>0</v>
+      </c>
+      <c r="CM15">
+        <v>0</v>
+      </c>
+      <c r="CN15">
+        <v>0</v>
+      </c>
+      <c r="CO15">
+        <v>0</v>
+      </c>
+      <c r="CP15">
+        <v>0</v>
+      </c>
+      <c r="CQ15">
+        <v>0</v>
+      </c>
+      <c r="CR15">
+        <v>0.0008041142207190496</v>
+      </c>
+      <c r="CS15">
+        <v>0</v>
+      </c>
+      <c r="CT15">
+        <v>0</v>
+      </c>
+      <c r="CU15">
+        <v>0</v>
+      </c>
+      <c r="CV15">
+        <v>0</v>
+      </c>
+      <c r="CW15">
+        <v>0.0008469943316900399</v>
+      </c>
+      <c r="CX15">
+        <v>0</v>
+      </c>
+      <c r="CY15">
+        <v>0</v>
+      </c>
+      <c r="CZ15">
+        <v>0</v>
+      </c>
+      <c r="DA15">
+        <v>0</v>
+      </c>
+      <c r="DB15">
+        <v>0</v>
+      </c>
+      <c r="DC15">
+        <v>0</v>
+      </c>
+      <c r="DD15">
+        <v>0</v>
+      </c>
+      <c r="DE15">
+        <v>0</v>
+      </c>
+      <c r="DF15">
+        <v>0</v>
+      </c>
+      <c r="DG15">
+        <v>0.0310929052740647</v>
+      </c>
+      <c r="DH15">
+        <v>0</v>
+      </c>
+      <c r="DI15">
+        <v>0</v>
+      </c>
+      <c r="DJ15">
+        <v>0</v>
+      </c>
+      <c r="DK15">
+        <v>0</v>
+      </c>
+      <c r="DL15">
+        <v>0</v>
+      </c>
+      <c r="DM15">
+        <v>0</v>
+      </c>
+      <c r="DN15">
+        <v>0</v>
+      </c>
+      <c r="DO15">
+        <v>0</v>
+      </c>
+      <c r="DP15">
+        <v>0</v>
+      </c>
+      <c r="DQ15">
+        <v>0</v>
+      </c>
+      <c r="DR15">
+        <v>0</v>
+      </c>
+      <c r="DS15">
+        <v>0</v>
+      </c>
+      <c r="DT15">
+        <v>0</v>
+      </c>
+      <c r="DU15">
+        <v>0</v>
+      </c>
+      <c r="DV15">
+        <v>0</v>
+      </c>
+      <c r="DW15">
+        <v>0.01504846363976714</v>
+      </c>
+      <c r="DX15">
+        <v>0</v>
+      </c>
+      <c r="DY15">
+        <v>0</v>
+      </c>
+      <c r="DZ15">
+        <v>0</v>
+      </c>
+      <c r="EA15">
+        <v>0</v>
+      </c>
+      <c r="EB15">
+        <v>0</v>
+      </c>
+      <c r="EC15">
+        <v>0</v>
+      </c>
+      <c r="ED15">
+        <v>0.0001657249287234022</v>
+      </c>
+      <c r="EE15">
+        <v>0</v>
+      </c>
+      <c r="EF15">
+        <v>0</v>
+      </c>
+      <c r="EG15">
+        <v>0</v>
+      </c>
+      <c r="EH15">
+        <v>0</v>
+      </c>
+      <c r="EI15">
+        <v>0</v>
+      </c>
+      <c r="EJ15">
+        <v>0</v>
+      </c>
+      <c r="EK15">
+        <v>0</v>
+      </c>
+      <c r="EL15">
+        <v>0</v>
+      </c>
+      <c r="EM15">
+        <v>0</v>
+      </c>
+      <c r="EN15">
+        <v>0</v>
+      </c>
+      <c r="EO15">
+        <v>0</v>
+      </c>
+      <c r="EP15">
+        <v>0</v>
+      </c>
+      <c r="EQ15">
+        <v>0</v>
+      </c>
+      <c r="ER15">
+        <v>0</v>
+      </c>
+      <c r="ES15">
+        <v>0</v>
+      </c>
+      <c r="ET15">
+        <v>0</v>
+      </c>
+      <c r="EU15">
+        <v>0</v>
+      </c>
+      <c r="EV15">
+        <v>0</v>
+      </c>
+      <c r="EW15">
+        <v>0</v>
+      </c>
+      <c r="EX15">
+        <v>0</v>
+      </c>
+      <c r="EY15">
+        <v>0</v>
+      </c>
+      <c r="EZ15">
+        <v>0</v>
+      </c>
+      <c r="FA15">
+        <v>0</v>
+      </c>
+      <c r="FB15">
+        <v>0</v>
+      </c>
+      <c r="FC15">
+        <v>0.04251218722223116</v>
+      </c>
+      <c r="FD15">
+        <v>0</v>
+      </c>
+      <c r="FE15">
+        <v>0</v>
+      </c>
+      <c r="FF15">
+        <v>0</v>
+      </c>
+      <c r="FG15">
+        <v>0</v>
+      </c>
+      <c r="FH15">
+        <v>0</v>
+      </c>
+      <c r="FI15">
+        <v>0</v>
+      </c>
+      <c r="FJ15">
+        <v>0</v>
+      </c>
+      <c r="FK15">
+        <v>0</v>
+      </c>
+      <c r="FL15">
+        <v>0</v>
+      </c>
+      <c r="FM15">
+        <v>0</v>
+      </c>
+      <c r="FN15">
+        <v>0</v>
+      </c>
+      <c r="FO15">
+        <v>0</v>
+      </c>
+      <c r="FP15">
+        <v>0</v>
+      </c>
+      <c r="FQ15">
+        <v>0</v>
+      </c>
+      <c r="FR15">
+        <v>0</v>
+      </c>
+      <c r="FS15">
+        <v>0</v>
+      </c>
+      <c r="FT15">
+        <v>0</v>
+      </c>
+      <c r="FU15">
+        <v>0</v>
+      </c>
+      <c r="FV15">
+        <v>0</v>
+      </c>
+      <c r="FW15">
+        <v>0</v>
+      </c>
+      <c r="FX15">
+        <v>0</v>
+      </c>
+      <c r="FY15">
+        <v>0</v>
+      </c>
+      <c r="FZ15">
+        <v>0</v>
+      </c>
+      <c r="GA15">
+        <v>0</v>
+      </c>
+      <c r="GB15">
+        <v>0</v>
+      </c>
+      <c r="GC15">
+        <v>0</v>
+      </c>
+      <c r="GD15">
+        <v>0</v>
+      </c>
+      <c r="GE15">
+        <v>0</v>
+      </c>
+      <c r="GF15">
+        <v>0</v>
+      </c>
+      <c r="GG15">
+        <v>0</v>
+      </c>
+      <c r="GH15">
+        <v>0</v>
+      </c>
+      <c r="GI15">
+        <v>0</v>
+      </c>
+      <c r="GJ15">
+        <v>0</v>
+      </c>
+      <c r="GK15">
+        <v>0</v>
+      </c>
+      <c r="GL15">
+        <v>0</v>
+      </c>
+      <c r="GM15">
+        <v>0</v>
+      </c>
+      <c r="GN15">
+        <v>0</v>
+      </c>
+      <c r="GO15">
+        <v>0</v>
+      </c>
+      <c r="GP15">
+        <v>0</v>
+      </c>
+      <c r="GQ15">
+        <v>0</v>
+      </c>
+      <c r="GR15">
+        <v>0</v>
+      </c>
+      <c r="GS15">
+        <v>0</v>
+      </c>
+      <c r="GT15">
+        <v>0</v>
+      </c>
+      <c r="GU15">
+        <v>0</v>
+      </c>
+      <c r="GV15">
+        <v>0</v>
+      </c>
+      <c r="GW15">
+        <v>0</v>
+      </c>
+      <c r="GX15">
+        <v>0</v>
+      </c>
+      <c r="GY15">
+        <v>0</v>
+      </c>
+      <c r="GZ15">
+        <v>40.514</v>
+      </c>
+      <c r="HA15">
+        <v>0</v>
+      </c>
+      <c r="HB15">
+        <v>0</v>
+      </c>
+      <c r="HC15">
+        <v>0</v>
+      </c>
+      <c r="HD15">
+        <v>100021440850</v>
+      </c>
+      <c r="HE15">
+        <v>0</v>
+      </c>
+      <c r="HF15">
+        <v>0</v>
+      </c>
+      <c r="HG15">
+        <v>0</v>
+      </c>
+      <c r="HH15">
+        <v>0</v>
+      </c>
+      <c r="HI15">
+        <v>0</v>
+      </c>
+      <c r="HJ15">
+        <v>0</v>
+      </c>
+      <c r="HK15">
+        <v>0</v>
+      </c>
+      <c r="HL15">
+        <v>0</v>
+      </c>
+      <c r="HM15">
+        <v>0</v>
+      </c>
+      <c r="HN15">
+        <v>0</v>
+      </c>
+      <c r="HO15">
+        <v>0</v>
+      </c>
+      <c r="HP15">
+        <v>0</v>
+      </c>
+      <c r="HQ15">
+        <v>0</v>
+      </c>
+      <c r="HR15">
+        <v>0</v>
+      </c>
+      <c r="HS15">
+        <v>0</v>
+      </c>
+      <c r="HT15">
+        <v>0</v>
+      </c>
+      <c r="HU15">
+        <v>0</v>
+      </c>
+      <c r="HV15">
+        <v>0</v>
+      </c>
+      <c r="HW15">
+        <v>0</v>
+      </c>
+      <c r="HX15">
+        <v>0</v>
+      </c>
+      <c r="HY15">
+        <v>0</v>
+      </c>
+      <c r="HZ15">
+        <v>0</v>
+      </c>
+      <c r="IA15">
+        <v>0</v>
+      </c>
+      <c r="IB15">
+        <v>0</v>
+      </c>
+      <c r="IC15">
+        <v>0</v>
+      </c>
+      <c r="ID15">
+        <v>0</v>
+      </c>
+      <c r="IE15">
+        <v>0</v>
+      </c>
+      <c r="IF15">
+        <v>0</v>
+      </c>
+      <c r="IG15">
+        <v>0</v>
+      </c>
+      <c r="IH15">
+        <v>0</v>
+      </c>
+      <c r="II15">
+        <v>0</v>
+      </c>
+      <c r="IJ15">
+        <v>0</v>
+      </c>
+      <c r="IK15">
+        <v>0</v>
+      </c>
+      <c r="IL15">
+        <v>0</v>
+      </c>
+      <c r="IM15">
+        <v>0</v>
+      </c>
+      <c r="IN15">
+        <v>0</v>
+      </c>
+      <c r="IO15">
+        <v>0</v>
+      </c>
+      <c r="IP15">
+        <v>0</v>
+      </c>
+      <c r="IQ15">
+        <v>0</v>
+      </c>
+      <c r="IR15">
+        <v>0</v>
+      </c>
+      <c r="IS15">
+        <v>0</v>
+      </c>
+      <c r="IT15">
+        <v>0</v>
+      </c>
+      <c r="IU15">
+        <v>0</v>
+      </c>
+      <c r="IV15">
+        <v>0</v>
+      </c>
+      <c r="IW15">
+        <v>0</v>
+      </c>
+      <c r="IX15">
+        <v>0</v>
+      </c>
+      <c r="IY15">
+        <v>0</v>
+      </c>
+      <c r="IZ15">
+        <v>0</v>
+      </c>
+      <c r="JA15">
+        <v>503082294.588</v>
+      </c>
+      <c r="JB15">
+        <v>0</v>
+      </c>
+      <c r="JC15">
+        <v>1857517867.706</v>
+      </c>
+      <c r="JD15">
+        <v>197705981.05</v>
+      </c>
+      <c r="JE15">
+        <v>0</v>
+      </c>
+      <c r="JF15">
+        <v>67037765313.5</v>
+      </c>
+      <c r="JG15">
+        <v>0</v>
+      </c>
+      <c r="JH15">
+        <v>0</v>
+      </c>
+      <c r="JI15">
+        <v>0</v>
+      </c>
+      <c r="JJ15">
+        <v>0</v>
+      </c>
+      <c r="JK15">
+        <v>0</v>
+      </c>
+      <c r="JL15">
+        <v>120459718559.9</v>
+      </c>
+      <c r="JM15">
+        <v>0</v>
+      </c>
+      <c r="JN15">
+        <v>0</v>
+      </c>
+      <c r="JO15">
+        <v>0</v>
+      </c>
+      <c r="JP15">
+        <v>0</v>
+      </c>
+      <c r="JQ15">
+        <v>0</v>
+      </c>
+      <c r="JR15">
+        <v>0</v>
+      </c>
+      <c r="JS15">
+        <v>0</v>
+      </c>
+      <c r="JT15">
+        <v>256456990.313</v>
+      </c>
+      <c r="JU15">
+        <v>0</v>
+      </c>
+      <c r="JV15">
+        <v>0</v>
+      </c>
+      <c r="JW15">
+        <v>0</v>
+      </c>
+      <c r="JX15">
+        <v>0</v>
+      </c>
+      <c r="JY15">
+        <v>270132789</v>
+      </c>
+      <c r="JZ15">
+        <v>0</v>
+      </c>
+      <c r="KA15">
+        <v>0</v>
+      </c>
+      <c r="KB15">
+        <v>0</v>
+      </c>
+      <c r="KC15">
+        <v>0</v>
+      </c>
+      <c r="KD15">
+        <v>0</v>
+      </c>
+      <c r="KE15">
+        <v>0</v>
+      </c>
+      <c r="KF15">
+        <v>0</v>
+      </c>
+      <c r="KG15">
+        <v>0</v>
+      </c>
+      <c r="KH15">
+        <v>0</v>
+      </c>
+      <c r="KI15">
+        <v>9916492833</v>
+      </c>
+      <c r="KJ15">
+        <v>0</v>
+      </c>
+      <c r="KK15">
+        <v>0</v>
+      </c>
+      <c r="KL15">
+        <v>0</v>
+      </c>
+      <c r="KM15">
+        <v>0</v>
+      </c>
+      <c r="KN15">
+        <v>0</v>
+      </c>
+      <c r="KO15">
+        <v>0</v>
+      </c>
+      <c r="KP15">
+        <v>0</v>
+      </c>
+      <c r="KQ15">
+        <v>0</v>
+      </c>
+      <c r="KR15">
+        <v>0</v>
+      </c>
+      <c r="KS15">
+        <v>0</v>
+      </c>
+      <c r="KT15">
+        <v>0</v>
+      </c>
+      <c r="KU15">
+        <v>0</v>
+      </c>
+      <c r="KV15">
+        <v>0</v>
+      </c>
+      <c r="KW15">
+        <v>0</v>
+      </c>
+      <c r="KX15">
+        <v>0</v>
+      </c>
+      <c r="KY15">
+        <v>4799422264.213</v>
+      </c>
+      <c r="KZ15">
+        <v>0</v>
+      </c>
+      <c r="LA15">
+        <v>0</v>
+      </c>
+      <c r="LB15">
+        <v>0</v>
+      </c>
+      <c r="LC15">
+        <v>0</v>
+      </c>
+      <c r="LD15">
+        <v>0</v>
+      </c>
+      <c r="LE15">
+        <v>0</v>
+      </c>
+      <c r="LF15">
+        <v>52854825.03</v>
+      </c>
+      <c r="LG15">
+        <v>0</v>
+      </c>
+      <c r="LH15">
+        <v>0</v>
+      </c>
+      <c r="LI15">
+        <v>0</v>
+      </c>
+      <c r="LJ15">
+        <v>0</v>
+      </c>
+      <c r="LK15">
+        <v>0</v>
+      </c>
+      <c r="LL15">
+        <v>0</v>
+      </c>
+      <c r="LM15">
+        <v>0</v>
+      </c>
+      <c r="LN15">
+        <v>0</v>
+      </c>
+      <c r="LO15">
+        <v>0</v>
+      </c>
+      <c r="LP15">
+        <v>0</v>
+      </c>
+      <c r="LQ15">
+        <v>0</v>
+      </c>
+      <c r="LR15">
+        <v>0</v>
+      </c>
+      <c r="LS15">
+        <v>0</v>
+      </c>
+      <c r="LT15">
+        <v>0</v>
+      </c>
+      <c r="LU15">
+        <v>0</v>
+      </c>
+      <c r="LV15">
+        <v>0</v>
+      </c>
+      <c r="LW15">
+        <v>0</v>
+      </c>
+      <c r="LX15">
+        <v>0</v>
+      </c>
+      <c r="LY15">
+        <v>0</v>
+      </c>
+      <c r="LZ15">
+        <v>0</v>
+      </c>
+      <c r="MA15">
+        <v>0</v>
+      </c>
+      <c r="MB15">
+        <v>0</v>
+      </c>
+      <c r="MC15">
+        <v>0</v>
+      </c>
+      <c r="MD15">
+        <v>0</v>
+      </c>
+      <c r="ME15">
+        <v>13558456380.596</v>
+      </c>
+      <c r="MF15">
+        <v>0</v>
+      </c>
+      <c r="MG15">
+        <v>0</v>
+      </c>
+      <c r="MH15">
+        <v>0</v>
+      </c>
+      <c r="MI15">
+        <v>0</v>
+      </c>
+      <c r="MJ15">
+        <v>0</v>
+      </c>
+      <c r="MK15">
+        <v>0</v>
+      </c>
+      <c r="ML15">
+        <v>0</v>
+      </c>
+      <c r="MM15">
+        <v>0</v>
+      </c>
+      <c r="MN15">
+        <v>0</v>
+      </c>
+      <c r="MO15">
+        <v>0</v>
+      </c>
+      <c r="MP15">
+        <v>0</v>
+      </c>
+      <c r="MQ15">
+        <v>0</v>
+      </c>
+      <c r="MR15">
+        <v>0</v>
+      </c>
+      <c r="MS15">
+        <v>0</v>
+      </c>
+      <c r="MT15">
+        <v>0</v>
+      </c>
+      <c r="MU15">
+        <v>0</v>
+      </c>
+      <c r="MV15">
+        <v>0</v>
+      </c>
+      <c r="MW15">
+        <v>0</v>
+      </c>
+      <c r="MX15">
+        <v>0</v>
+      </c>
+      <c r="MY15">
+        <v>0</v>
+      </c>
+      <c r="MZ15">
+        <v>0</v>
+      </c>
+      <c r="NA15">
+        <v>0</v>
+      </c>
+      <c r="NB15">
+        <v>0</v>
+      </c>
+      <c r="NC15">
+        <v>0</v>
+      </c>
+      <c r="ND15">
+        <v>0</v>
+      </c>
+      <c r="NE15">
+        <v>0</v>
+      </c>
+      <c r="NF15">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C1:GD1"/>
